--- a/2026 New/results_quantile.xlsx
+++ b/2026 New/results_quantile.xlsx
@@ -191,7 +191,7 @@
     <t>Zakłady Mięsne Henryk Kania SA w upadłości | NIP 7440003325 | Removed from analysis | firms=1, rows=1 | Reason [LIQUIDATION]: Non-comparable financial statements due to liquidation.</t>
   </si>
   <si>
-    <t>Globus sp. z o.o., Warszawa | NIP 7773261746 | Removed from analysis | firms=1, rows=1 | Reason [EXTREME_PROFITABILITY_RATIO]: Extreme net-profit/sales ratio from a very small sales denominator; dominates profitability variation in regression analysis.</t>
+    <t>Globus sp. z o.o., Warszawa | NIP 7773261746 | Removed from analysis | firms=1, rows=1 | Reason [HOLDING_NONCONSOLIDATED]: Non-comparable financial statements: holding company reports non-consolidated financial statements.</t>
   </si>
   <si>
     <t>Nominal annualised log sales growth; measured in log points per year, rather than a log sales level or CAGR.</t>
@@ -5479,7 +5479,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="66" customHeight="1">
+    <row r="11" spans="1:2" ht="51" customHeight="1">
       <c r="A11" t="s">
         <v>11</v>
       </c>

--- a/2026 New/results_quantile.xlsx
+++ b/2026 New/results_quantile.xlsx
@@ -59,6 +59,93 @@
     <t>Growth mode</t>
   </si>
   <si>
+    <t>Dependent variable</t>
+  </si>
+  <si>
+    <t>Sales basis</t>
+  </si>
+  <si>
+    <t>Dependent variable P1</t>
+  </si>
+  <si>
+    <t>Dependent variable P2</t>
+  </si>
+  <si>
+    <t>Dependent variable P3</t>
+  </si>
+  <si>
+    <t>Dependent variable FULL</t>
+  </si>
+  <si>
+    <t>Dependent variable preparation</t>
+  </si>
+  <si>
+    <t>Quantiles</t>
+  </si>
+  <si>
+    <t>Preferred model variant</t>
+  </si>
+  <si>
+    <t>Shared model controls</t>
+  </si>
+  <si>
+    <t>Base regressors</t>
+  </si>
+  <si>
+    <t>Ownership</t>
+  </si>
+  <si>
+    <t>Winsorisation</t>
+  </si>
+  <si>
+    <t>Standardisation</t>
+  </si>
+  <si>
+    <t>Generated regressors by period</t>
+  </si>
+  <si>
+    <t>Estimator-specific inference</t>
+  </si>
+  <si>
+    <t>2018 role</t>
+  </si>
+  <si>
+    <t>Lag growth logic</t>
+  </si>
+  <si>
+    <t>Main analysis window</t>
+  </si>
+  <si>
+    <t>Sector controls</t>
+  </si>
+  <si>
+    <t>Model specification</t>
+  </si>
+  <si>
+    <t>Quantile interpretation</t>
+  </si>
+  <si>
+    <t>Performance framework anchors</t>
+  </si>
+  <si>
+    <t>Methodological caution</t>
+  </si>
+  <si>
+    <t>QuantReg estimation settings</t>
+  </si>
+  <si>
+    <t>Scenarios</t>
+  </si>
+  <si>
+    <t>Readable comparison sheets</t>
+  </si>
+  <si>
+    <t>Comparison column order</t>
+  </si>
+  <si>
+    <t>Quantile pattern classification</t>
+  </si>
+  <si>
     <t>Manual exclusions</t>
   </si>
   <si>
@@ -80,93 +167,6 @@
     <t>Manual exclusion 6</t>
   </si>
   <si>
-    <t>Dependent variable</t>
-  </si>
-  <si>
-    <t>Sales basis</t>
-  </si>
-  <si>
-    <t>Dependent variable P1</t>
-  </si>
-  <si>
-    <t>Dependent variable P2</t>
-  </si>
-  <si>
-    <t>Dependent variable P3</t>
-  </si>
-  <si>
-    <t>Dependent variable FULL</t>
-  </si>
-  <si>
-    <t>Dependent variable preparation</t>
-  </si>
-  <si>
-    <t>Quantiles</t>
-  </si>
-  <si>
-    <t>Preferred model variant</t>
-  </si>
-  <si>
-    <t>Shared model controls</t>
-  </si>
-  <si>
-    <t>Base regressors</t>
-  </si>
-  <si>
-    <t>Ownership</t>
-  </si>
-  <si>
-    <t>Winsorisation</t>
-  </si>
-  <si>
-    <t>Standardisation</t>
-  </si>
-  <si>
-    <t>Generated regressors by period</t>
-  </si>
-  <si>
-    <t>Estimator-specific inference</t>
-  </si>
-  <si>
-    <t>2018 role</t>
-  </si>
-  <si>
-    <t>Lag growth logic</t>
-  </si>
-  <si>
-    <t>Main analysis window</t>
-  </si>
-  <si>
-    <t>Sector controls</t>
-  </si>
-  <si>
-    <t>Model specification</t>
-  </si>
-  <si>
-    <t>Quantile interpretation</t>
-  </si>
-  <si>
-    <t>Performance framework anchors</t>
-  </si>
-  <si>
-    <t>Methodological caution</t>
-  </si>
-  <si>
-    <t>QuantReg estimation settings</t>
-  </si>
-  <si>
-    <t>Scenarios</t>
-  </si>
-  <si>
-    <t>Readable comparison sheets</t>
-  </si>
-  <si>
-    <t>Comparison column order</t>
-  </si>
-  <si>
-    <t>Quantile pattern classification</t>
-  </si>
-  <si>
     <t>period_quantile_regression</t>
   </si>
   <si>
@@ -179,6 +179,93 @@
     <t>nominal</t>
   </si>
   <si>
+    <t>Nominal annualised log sales growth; measured in log points per year, rather than a log sales level or CAGR.</t>
+  </si>
+  <si>
+    <t>Nominal sales at current prices (sales).</t>
+  </si>
+  <si>
+    <t>Nominal annualised log sales growth (2019-2020); source column: ngrowth_log_ann_P1; formula: (ln(sales_2020) - ln(sales_2019)) / 1.</t>
+  </si>
+  <si>
+    <t>Nominal annualised log sales growth (2020-2022); source column: ngrowth_log_ann_P2; formula: (ln(sales_2022) - ln(sales_2020)) / 2.</t>
+  </si>
+  <si>
+    <t>Nominal annualised log sales growth (2022-2024); source column: ngrowth_log_ann_P3; formula: (ln(sales_2024) - ln(sales_2022)) / 2.</t>
+  </si>
+  <si>
+    <t>Nominal annualised log sales growth (2019-2024); source column: ngrowth_log_ann_2019_2024; formula: (ln(sales_2024) - ln(sales_2019)) / 5.</t>
+  </si>
+  <si>
+    <t>The source growth variable is winsorised and then standardised within the scenario-period estimation sample according to the settings below. Logs require strictly positive endpoint sales; otherwise growth is missing.</t>
+  </si>
+  <si>
+    <t>0.1, 0.5, 0.9</t>
+  </si>
+  <si>
+    <t>winsor_std</t>
+  </si>
+  <si>
+    <t>code_config.PERIOD_MODEL_SETTINGS; design matrices and metadata use the same builders as OLS scenarios.</t>
+  </si>
+  <si>
+    <t>ln_sales, profit_margin, export_ratio, asset_turnover, capital_ratio, sales_per_employee</t>
+  </si>
+  <si>
+    <t>include_owner=True; column=owner_num</t>
+  </si>
+  <si>
+    <t>Dependent variable only; lower=0.01; upper=0.99 within each scenario-period estimation sample.</t>
+  </si>
+  <si>
+    <t>standardised_models=True; standardise_dependent=True; population standard deviation (ddof=0).</t>
+  </si>
+  <si>
+    <t>P1: ln_sales_start_P1, profit_margin_start_P1, export_ratio_start_P1, asset_turnover_start_P1, capital_ratio_start_P1, sales_per_employee_start_P1, owner_num, export_ratio_x_ln_sales_start_P1, lag_ngrowth_log_ann_P1; P2: ln_sales_start_P2, profit_margin_start_P2, export_ratio_start_P2, asset_turnover_start_P2, capital_ratio_start_P2, sales_per_employee_start_P2, owner_num, export_ratio_x_ln_sales_start_P2, lag_ngrowth_log_ann_P2; P3: ln_sales_start_P3, profit_margin_start_P3, export_ratio_start_P3, asset_turnover_start_P3, capital_ratio_start_P3, sales_per_employee_start_P3, owner_num, export_ratio_x_ln_sales_start_P3, lag_ngrowth_log_ann_P3; FULL: ln_sales_start_P1, profit_margin_start_P1, export_ratio_start_P1, asset_turnover_start_P1, capital_ratio_start_P1, sales_per_employee_start_P1, owner_num, export_ratio_x_ln_sales_start_P1</t>
+  </si>
+  <si>
+    <t>QuantReg retains its default robust covariance, Epanechnikov kernel and Hall-Sheather bandwidth. OLS covariance settings do not transfer directly between estimators.</t>
+  </si>
+  <si>
+    <t>2018 is used only to calculate P1 lag growth; it is not an analytical outcome period.</t>
+  </si>
+  <si>
+    <t>P1 uses 2018-2019 lag growth; P2 and P3 retain their prior-period lags; FULL has no lag growth.</t>
+  </si>
+  <si>
+    <t>Dependent variables, trajectories, SGrowth_NR, and FULL growth remain based on 2019-2024.</t>
+  </si>
+  <si>
+    <t>sector_en is required and included as a categorical control with production as the reference category.</t>
+  </si>
+  <si>
+    <t>winsorised dependent variable and standardised numeric regressors/dependent variable</t>
+  </si>
+  <si>
+    <t>Quantile regression estimates conditional quantile relationships rather than fixed firm groups.</t>
+  </si>
+  <si>
+    <t>The quantiles are interpreted as anchors within the broader four-zone performance framework: below Q10 -&gt; Bottom 10%; Q10-Q50 -&gt; moderate decline / lower-middle performance; Q50-Q90 -&gt; moderate growth / upper-middle performance; above Q90 -&gt; Top 10%.</t>
+  </si>
+  <si>
+    <t>Quantile-regression standard errors and p-values may be sensitive to heteroskedasticity, extreme observations, and large dummy-variable structures. Coefficient direction, relative magnitude, and cross-quantile comparison should often be interpreted more cautiously than exact significance thresholds.</t>
+  </si>
+  <si>
+    <t>Quantile regression estimation uses max_iter=5000 and p_tol=1e-06 due to the complexity of sector dummy structures, interaction terms, and skewed firm-level distributions. Convergence warnings do not necessarily invalidate coefficient estimates, but should be interpreted cautiously.</t>
+  </si>
+  <si>
+    <t>ALL: All firms; shared sample: All; MANUFACTURING: manufacturing == 1; RANK2019: 2019 ranking firms; shared sample: Rank2019; RANK2019_MANUFACTURING: 2019 ranking manufacturing firms; shared sample: Rank2019_Manufacturing</t>
+  </si>
+  <si>
+    <t>Readable comparison sheets are split by period: Compare_FULL, Compare_P1, Compare_P2, and Compare_P3.</t>
+  </si>
+  <si>
+    <t>Each comparison sheet orders columns by scenario order -&gt; quantile order. Scenario order in readable comparison sheets: ALL -&gt; MANUFACTURING -&gt; RANK2019 -&gt; RANK2019_MANUFACTURING. This avoids misleading alphabetical ordering of scenario-period-quantile columns.</t>
+  </si>
+  <si>
+    <t>Quantile pattern classification is descriptive only. It is based on coefficient direction and relative size across Q10, Q50 and Q90. It is not a formal statistical test.</t>
+  </si>
+  <si>
     <t>Enabled=True. Shared code_config.MANUAL_EXCLUSIONS; match verified NIP or exact company name (outer whitespace ignored). Applied before analytical filtering and all transformations. Canonical data retained.</t>
   </si>
   <si>
@@ -198,93 +285,6 @@
   </si>
   <si>
     <t>Ordipol sp. z o.o. (w upadłości), Bielany Wrocławskie | NIP 6772001669 | Removed from analysis | firms=1, rows=1 | Reason [LIQUIDATION]: Non-comparable financial statements due to liquidation.</t>
-  </si>
-  <si>
-    <t>Nominal annualised log sales growth; measured in log points per year, rather than a log sales level or CAGR.</t>
-  </si>
-  <si>
-    <t>Nominal sales at current prices (sales).</t>
-  </si>
-  <si>
-    <t>Nominal annualised log sales growth (2019-2020); source column: ngrowth_log_ann_P1; formula: (ln(sales_2020) - ln(sales_2019)) / 1.</t>
-  </si>
-  <si>
-    <t>Nominal annualised log sales growth (2020-2022); source column: ngrowth_log_ann_P2; formula: (ln(sales_2022) - ln(sales_2020)) / 2.</t>
-  </si>
-  <si>
-    <t>Nominal annualised log sales growth (2022-2024); source column: ngrowth_log_ann_P3; formula: (ln(sales_2024) - ln(sales_2022)) / 2.</t>
-  </si>
-  <si>
-    <t>Nominal annualised log sales growth (2019-2024); source column: ngrowth_log_ann_2019_2024; formula: (ln(sales_2024) - ln(sales_2019)) / 5.</t>
-  </si>
-  <si>
-    <t>The source growth variable is winsorised and then standardised within the scenario-period estimation sample according to the settings below. Logs require strictly positive endpoint sales; otherwise growth is missing.</t>
-  </si>
-  <si>
-    <t>0.1, 0.5, 0.9</t>
-  </si>
-  <si>
-    <t>winsor_std</t>
-  </si>
-  <si>
-    <t>code_config.PERIOD_MODEL_SETTINGS; design matrices and metadata use the same builders as OLS scenarios.</t>
-  </si>
-  <si>
-    <t>ln_sales, profit_margin, export_ratio, asset_turnover, capital_ratio, sales_per_employee</t>
-  </si>
-  <si>
-    <t>include_owner=True; column=owner_num</t>
-  </si>
-  <si>
-    <t>Dependent variable only; lower=0.01; upper=0.99 within each scenario-period estimation sample.</t>
-  </si>
-  <si>
-    <t>standardised_models=True; standardise_dependent=True; population standard deviation (ddof=0).</t>
-  </si>
-  <si>
-    <t>P1: ln_sales_start_P1, profit_margin_start_P1, export_ratio_start_P1, asset_turnover_start_P1, capital_ratio_start_P1, sales_per_employee_start_P1, owner_num, export_ratio_x_ln_sales_start_P1, lag_ngrowth_log_ann_P1; P2: ln_sales_start_P2, profit_margin_start_P2, export_ratio_start_P2, asset_turnover_start_P2, capital_ratio_start_P2, sales_per_employee_start_P2, owner_num, export_ratio_x_ln_sales_start_P2, lag_ngrowth_log_ann_P2; P3: ln_sales_start_P3, profit_margin_start_P3, export_ratio_start_P3, asset_turnover_start_P3, capital_ratio_start_P3, sales_per_employee_start_P3, owner_num, export_ratio_x_ln_sales_start_P3, lag_ngrowth_log_ann_P3; FULL: ln_sales_start_P1, profit_margin_start_P1, export_ratio_start_P1, asset_turnover_start_P1, capital_ratio_start_P1, sales_per_employee_start_P1, owner_num, export_ratio_x_ln_sales_start_P1</t>
-  </si>
-  <si>
-    <t>QuantReg retains its default robust covariance, Epanechnikov kernel and Hall-Sheather bandwidth. OLS covariance settings do not transfer directly between estimators.</t>
-  </si>
-  <si>
-    <t>2018 is used only to calculate P1 lag growth; it is not an analytical outcome period.</t>
-  </si>
-  <si>
-    <t>P1 uses 2018-2019 lag growth; P2 and P3 retain their prior-period lags; FULL has no lag growth.</t>
-  </si>
-  <si>
-    <t>Dependent variables, trajectories, SGrowth_NR, and FULL growth remain based on 2019-2024.</t>
-  </si>
-  <si>
-    <t>sector_en is required and included as a categorical control with production as the reference category.</t>
-  </si>
-  <si>
-    <t>winsorised dependent variable and standardised numeric regressors/dependent variable</t>
-  </si>
-  <si>
-    <t>Quantile regression estimates conditional quantile relationships rather than fixed firm groups.</t>
-  </si>
-  <si>
-    <t>The quantiles are interpreted as anchors within the broader four-zone performance framework: below Q10 -&gt; Bottom 10%; Q10-Q50 -&gt; moderate decline / lower-middle performance; Q50-Q90 -&gt; moderate growth / upper-middle performance; above Q90 -&gt; Top 10%.</t>
-  </si>
-  <si>
-    <t>Quantile-regression standard errors and p-values may be sensitive to heteroskedasticity, extreme observations, and large dummy-variable structures. Coefficient direction, relative magnitude, and cross-quantile comparison should often be interpreted more cautiously than exact significance thresholds.</t>
-  </si>
-  <si>
-    <t>Quantile regression estimation uses max_iter=5000 and p_tol=1e-06 due to the complexity of sector dummy structures, interaction terms, and skewed firm-level distributions. Convergence warnings do not necessarily invalidate coefficient estimates, but should be interpreted cautiously.</t>
-  </si>
-  <si>
-    <t>ALL: All firms; shared sample: All; MANUFACTURING: manufacturing == 1; RANK2019: 2019 ranking firms; shared sample: Rank2019; RANK2019_MANUFACTURING: 2019 ranking manufacturing firms; shared sample: Rank2019_Manufacturing</t>
-  </si>
-  <si>
-    <t>Readable comparison sheets are split by period: Compare_FULL, Compare_P1, Compare_P2, and Compare_P3.</t>
-  </si>
-  <si>
-    <t>Each comparison sheet orders columns by scenario order -&gt; quantile order. Scenario order in readable comparison sheets: ALL -&gt; MANUFACTURING -&gt; RANK2019 -&gt; RANK2019_MANUFACTURING. This avoids misleading alphabetical ordering of scenario-period-quantile columns.</t>
-  </si>
-  <si>
-    <t>Quantile pattern classification is descriptive only. It is based on coefficient direction and relative size across Q10, Q50 and Q90. It is not a formal statistical test.</t>
   </si>
   <si>
     <t>display_name</t>
@@ -5449,7 +5449,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="51" customHeight="1">
+    <row r="6" spans="1:2" ht="36" customHeight="1">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="51" customHeight="1">
+    <row r="7" spans="1:2" ht="21" customHeight="1">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="66" customHeight="1">
+    <row r="8" spans="1:2" ht="36" customHeight="1">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -5473,7 +5473,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="51" customHeight="1">
+    <row r="9" spans="1:2" ht="36" customHeight="1">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="51" customHeight="1">
+    <row r="10" spans="1:2" ht="36" customHeight="1">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -5489,7 +5489,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="51" customHeight="1">
+    <row r="11" spans="1:2" ht="36" customHeight="1">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -5505,7 +5505,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="36" customHeight="1">
+    <row r="13" spans="1:2" ht="21" customHeight="1">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="36" customHeight="1">
+    <row r="17" spans="1:2" ht="21" customHeight="1">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="51" customHeight="1">
+    <row r="19" spans="1:2" ht="36" customHeight="1">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -5561,7 +5561,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="21" customHeight="1">
+    <row r="20" spans="1:2" ht="186" customHeight="1">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="21" customHeight="1">
+    <row r="21" spans="1:2" ht="51" customHeight="1">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="21" customHeight="1">
+    <row r="24" spans="1:2" ht="36" customHeight="1">
       <c r="A24" t="s">
         <v>24</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="186" customHeight="1">
+    <row r="27" spans="1:2" ht="36" customHeight="1">
       <c r="A27" t="s">
         <v>27</v>
       </c>
@@ -5625,7 +5625,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="51" customHeight="1">
+    <row r="28" spans="1:2" ht="66" customHeight="1">
       <c r="A28" t="s">
         <v>28</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="36" customHeight="1">
+    <row r="29" spans="1:2" ht="81" customHeight="1">
       <c r="A29" t="s">
         <v>29</v>
       </c>
@@ -5641,7 +5641,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="36" customHeight="1">
+    <row r="30" spans="1:2" ht="66" customHeight="1">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="36" customHeight="1">
+    <row r="31" spans="1:2" ht="66" customHeight="1">
       <c r="A31" t="s">
         <v>31</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="36" customHeight="1">
+    <row r="33" spans="1:2" ht="66" customHeight="1">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -5673,7 +5673,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="36" customHeight="1">
+    <row r="34" spans="1:2" ht="51" customHeight="1">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -5681,7 +5681,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="66" customHeight="1">
+    <row r="35" spans="1:2" ht="51" customHeight="1">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -5689,7 +5689,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="81" customHeight="1">
+    <row r="36" spans="1:2" ht="51" customHeight="1">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -5705,7 +5705,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="66" customHeight="1">
+    <row r="38" spans="1:2" ht="51" customHeight="1">
       <c r="A38" t="s">
         <v>38</v>
       </c>
@@ -5713,7 +5713,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="36" customHeight="1">
+    <row r="39" spans="1:2" ht="51" customHeight="1">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="66" customHeight="1">
+    <row r="40" spans="1:2" ht="51" customHeight="1">
       <c r="A40" t="s">
         <v>40</v>
       </c>
@@ -10689,7 +10689,7 @@
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>120</v>
@@ -11724,7 +11724,7 @@
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>372</v>
@@ -12800,7 +12800,7 @@
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>631</v>
@@ -13876,7 +13876,7 @@
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>890</v>

--- a/2026 New/results_quantile.xlsx
+++ b/2026 New/results_quantile.xlsx
@@ -5043,7 +5043,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5058,6 +5058,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -5092,7 +5105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -5102,6 +5115,21 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="center" wrapText="1" horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center" horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1" vertical="center" horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10648,1024 +10676,1035 @@
   <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
-    <col min="2" max="13" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" ht="36.0" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="8" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A4" t="s" s="7">
         <v>98</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="8">
         <v>124</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="8">
         <v>124</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="8">
         <v>124</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="8">
         <v>194</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="8">
         <v>194</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="8">
         <v>194</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="8">
         <v>249</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="8">
         <v>249</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="8">
         <v>249</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="s" s="8">
         <v>317</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" t="s" s="8">
         <v>317</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" t="s" s="8">
         <v>317</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A5" t="s" s="7">
         <v>99</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="8">
         <v>125</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="8">
         <v>148</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="8">
         <v>171</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="8">
         <v>195</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="8">
         <v>213</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="8">
         <v>231</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="8">
         <v>250</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="8">
         <v>273</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="8">
         <v>295</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="8">
         <v>318</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" t="s" s="8">
         <v>336</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" t="s" s="8">
         <v>354</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A6" t="s" s="7">
         <v>100</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="8">
         <v>126</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="8">
         <v>149</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="8">
         <v>172</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="8">
         <v>196</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="8">
         <v>214</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="8">
         <v>232</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" t="s" s="8">
         <v>251</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="8">
         <v>274</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" t="s" s="8">
         <v>296</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="8">
         <v>319</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" t="s" s="8">
         <v>337</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" t="s" s="8">
         <v>355</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A7" t="s" s="7">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="8">
         <v>127</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="8">
         <v>150</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="8">
         <v>173</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="8">
         <v>197</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="8">
         <v>215</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" t="s" s="8">
         <v>233</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" t="s" s="8">
         <v>252</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="8">
         <v>275</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" t="s" s="8">
         <v>297</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="s" s="8">
         <v>320</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="s" s="8">
         <v>338</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" t="s" s="8">
         <v>356</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A8" t="s" s="7">
         <v>102</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="8">
         <v>128</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="8">
         <v>151</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="8">
         <v>174</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="8">
         <v>198</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="8">
         <v>216</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" t="s" s="8">
         <v>234</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" t="s" s="8">
         <v>253</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="8">
         <v>276</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" t="s" s="8">
         <v>298</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" t="s" s="8">
         <v>321</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" t="s" s="8">
         <v>339</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" t="s" s="8">
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A9" t="s" s="7">
         <v>103</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="8">
         <v>129</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="8">
         <v>152</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="8">
         <v>175</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="8">
         <v>199</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="8">
         <v>217</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" t="s" s="8">
         <v>235</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" t="s" s="8">
         <v>254</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="8">
         <v>277</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" t="s" s="8">
         <v>299</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="s" s="8">
         <v>322</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="s" s="8">
         <v>340</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" t="s" s="8">
         <v>358</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A10" t="s" s="7">
         <v>104</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="8">
         <v>130</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="8">
         <v>153</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="8">
         <v>176</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="8">
         <v>200</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="8">
         <v>218</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" t="s" s="8">
         <v>236</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" t="s" s="8">
         <v>255</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" t="s" s="8">
         <v>278</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" t="s" s="8">
         <v>300</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="s" s="8">
         <v>323</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" t="s" s="8">
         <v>341</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" t="s" s="8">
         <v>359</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A11" t="s" s="7">
         <v>105</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="8">
         <v>131</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="8">
         <v>154</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="8">
         <v>177</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="8">
         <v>201</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="8">
         <v>219</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" t="s" s="8">
         <v>237</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" t="s" s="8">
         <v>256</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" t="s" s="8">
         <v>130</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" t="s" s="8">
         <v>301</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="s" s="8">
         <v>324</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" t="s" s="8">
         <v>342</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" t="s" s="8">
         <v>360</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A12" t="s" s="7">
         <v>106</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="8">
         <v>132</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="8">
         <v>155</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="8">
         <v>178</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="8">
         <v>202</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="8">
         <v>220</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" t="s" s="8">
         <v>238</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" t="s" s="8">
         <v>257</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" t="s" s="8">
         <v>279</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" t="s" s="8">
         <v>302</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" t="s" s="8">
         <v>325</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" t="s" s="8">
         <v>343</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" t="s" s="8">
         <v>361</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
+    <row r="13" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A13" t="s" s="7">
         <v>107</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="8">
         <v>133</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="8">
         <v>156</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="8">
         <v>179</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="8">
         <v>203</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="8">
         <v>221</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="8">
         <v>239</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="s" s="8">
         <v>258</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" t="s" s="8">
         <v>280</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" t="s" s="8">
         <v>303</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="s" s="8">
         <v>326</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" t="s" s="8">
         <v>344</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" t="s" s="8">
         <v>362</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
+    <row r="14" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A14" t="s" s="7">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="8">
         <v>134</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="8">
         <v>157</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="8">
         <v>180</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="8">
         <v>204</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="8">
         <v>222</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="8">
         <v>240</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" t="s" s="8">
         <v>259</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" t="s" s="8">
         <v>281</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" t="s" s="8">
         <v>304</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="s" s="8">
         <v>327</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" t="s" s="8">
         <v>345</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" t="s" s="8">
         <v>363</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A15" t="s" s="7">
         <v>109</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="8">
         <v>135</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="8">
         <v>158</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="8">
         <v>181</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="8">
         <v>205</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="8">
         <v>223</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="8">
         <v>241</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" t="s" s="8">
         <v>260</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" t="s" s="8">
         <v>282</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" t="s" s="8">
         <v>288</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" t="s" s="8">
         <v>328</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" t="s" s="8">
         <v>346</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" t="s" s="8">
         <v>364</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A16" t="s" s="7">
         <v>110</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="8">
         <v>136</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="8">
         <v>159</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="8">
         <v>182</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="8">
         <v>206</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="8">
         <v>224</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="8">
         <v>242</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" t="s" s="8">
         <v>261</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" t="s" s="8">
         <v>283</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" t="s" s="8">
         <v>305</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" t="s" s="8">
         <v>329</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" t="s" s="8">
         <v>347</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" t="s" s="8">
         <v>365</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A17" t="s" s="7">
         <v>111</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="8">
         <v>137</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="8">
         <v>160</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="8">
         <v>183</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="8">
         <v>207</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="8">
         <v>225</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="8">
         <v>243</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" t="s" s="8">
         <v>262</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" t="s" s="8">
         <v>284</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" t="s" s="8">
         <v>306</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" t="s" s="8">
         <v>330</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" t="s" s="8">
         <v>348</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" t="s" s="8">
         <v>366</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
+    <row r="18" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A18" t="s" s="7">
         <v>112</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="8">
         <v>138</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="8">
         <v>161</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="8">
         <v>184</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" t="s" s="8">
         <v>263</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" t="s" s="8">
         <v>285</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" t="s" s="8">
         <v>307</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
+    <row r="19" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A19" t="s" s="7">
         <v>113</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="8">
         <v>139</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="8">
         <v>162</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="8">
         <v>185</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" t="s" s="8">
         <v>208</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" t="s" s="8">
         <v>226</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" t="s" s="8">
         <v>244</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" t="s" s="8">
         <v>264</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" t="s" s="8">
         <v>286</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" t="s" s="8">
         <v>308</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" t="s" s="8">
         <v>331</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" t="s" s="8">
         <v>349</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" t="s" s="8">
         <v>367</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
+    <row r="20" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A20" t="s" s="7">
         <v>114</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="8">
         <v>140</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="8">
         <v>163</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="8">
         <v>186</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="8">
         <v>209</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="8">
         <v>227</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" t="s" s="8">
         <v>245</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" t="s" s="8">
         <v>265</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" t="s" s="8">
         <v>287</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" t="s" s="8">
         <v>309</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="s" s="8">
         <v>332</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" t="s" s="8">
         <v>350</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" t="s" s="8">
         <v>368</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
+    <row r="21" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A21" t="s" s="7">
         <v>115</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="8">
         <v>141</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="8">
         <v>164</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="8">
         <v>187</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="8">
         <v>210</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="8">
         <v>228</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" t="s" s="8">
         <v>246</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" t="s" s="8">
         <v>266</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" t="s" s="8">
         <v>288</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" t="s" s="8">
         <v>310</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" t="s" s="8">
         <v>333</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" t="s" s="8">
         <v>351</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" t="s" s="8">
         <v>369</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
+    <row r="22" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A22" t="s" s="7">
         <v>116</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="8">
         <v>142</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="8">
         <v>165</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="8">
         <v>188</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" t="s" s="8">
         <v>267</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" t="s" s="8">
         <v>289</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" t="s" s="8">
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
+    <row r="23" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A23" t="s" s="7">
         <v>117</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="8">
         <v>143</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="8">
         <v>166</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="8">
         <v>189</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E23" t="s" s="8">
         <v>211</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" t="s" s="8">
         <v>229</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G23" t="s" s="8">
         <v>247</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="s" s="8">
         <v>268</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="8">
         <v>290</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" t="s" s="8">
         <v>312</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" t="s" s="8">
         <v>334</v>
       </c>
-      <c r="L23" t="s">
+      <c r="L23" t="s" s="8">
         <v>352</v>
       </c>
-      <c r="M23" t="s">
+      <c r="M23" t="s" s="8">
         <v>370</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
+    <row r="24" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A24" t="s" s="7">
         <v>118</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="8">
         <v>144</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="8">
         <v>167</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="8">
         <v>190</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" t="s" s="8">
         <v>269</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" t="s" s="8">
         <v>291</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" t="s" s="8">
         <v>313</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
+    <row r="25" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A25" t="s" s="7">
         <v>119</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="8">
         <v>145</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="8">
         <v>168</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="8">
         <v>191</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" t="s" s="8">
         <v>212</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F25" t="s" s="8">
         <v>230</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" t="s" s="8">
         <v>248</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" t="s" s="8">
         <v>270</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" t="s" s="8">
         <v>292</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" t="s" s="8">
         <v>314</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K25" t="s" s="8">
         <v>335</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" t="s" s="8">
         <v>353</v>
       </c>
-      <c r="M25" t="s">
+      <c r="M25" t="s" s="8">
         <v>371</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
+    <row r="26" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A26" t="s" s="7">
         <v>120</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="8">
         <v>146</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" t="s" s="8">
         <v>169</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="s" s="8">
         <v>192</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" t="s" s="8">
         <v>271</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" t="s" s="8">
         <v>293</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" t="s" s="8">
         <v>315</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
+    <row r="27" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A27" t="s" s="7">
         <v>121</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="8">
         <v>147</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" t="s" s="8">
         <v>170</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="8">
         <v>193</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" t="s" s="8">
         <v>272</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" t="s" s="8">
         <v>294</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" t="s" s="8">
         <v>316</v>
       </c>
     </row>
@@ -11683,1065 +11722,1076 @@
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
-    <col min="2" max="13" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" ht="36.0" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="8" t="s">
         <v>373</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="8" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="8" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A4" t="s" s="7">
         <v>98</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="8">
         <v>375</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="8">
         <v>375</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="8">
         <v>375</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="8">
         <v>446</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="8">
         <v>446</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="8">
         <v>446</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="8">
         <v>503</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="8">
         <v>503</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="8">
         <v>503</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="s" s="8">
         <v>574</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" t="s" s="8">
         <v>574</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" t="s" s="8">
         <v>574</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A5" t="s" s="7">
         <v>99</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="8">
         <v>376</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="8">
         <v>399</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="8">
         <v>422</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="8">
         <v>447</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="8">
         <v>466</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="8">
         <v>484</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="8">
         <v>504</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="8">
         <v>528</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="8">
         <v>399</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="8">
         <v>575</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" t="s" s="8">
         <v>594</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" t="s" s="8">
         <v>613</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A6" t="s" s="7">
         <v>100</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="8">
         <v>212</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="8">
         <v>400</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="8">
         <v>423</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="8">
         <v>448</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="8">
         <v>467</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="8">
         <v>485</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" t="s" s="8">
         <v>505</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="8">
         <v>529</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" t="s" s="8">
         <v>551</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="8">
         <v>576</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" t="s" s="8">
         <v>595</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" t="s" s="8">
         <v>614</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A7" t="s" s="7">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="8">
         <v>377</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="8">
         <v>401</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="8">
         <v>424</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="8">
         <v>449</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="8">
         <v>468</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" t="s" s="8">
         <v>486</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" t="s" s="8">
         <v>506</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="8">
         <v>530</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" t="s" s="8">
         <v>552</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="s" s="8">
         <v>577</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="s" s="8">
         <v>596</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" t="s" s="8">
         <v>615</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A8" t="s" s="7">
         <v>102</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="8">
         <v>378</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="8">
         <v>402</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="8">
         <v>425</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="8">
         <v>450</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="8">
         <v>469</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" t="s" s="8">
         <v>487</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" t="s" s="8">
         <v>507</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="8">
         <v>531</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" t="s" s="8">
         <v>553</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" t="s" s="8">
         <v>578</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" t="s" s="8">
         <v>597</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" t="s" s="8">
         <v>616</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A9" t="s" s="7">
         <v>103</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="8">
         <v>379</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="8">
         <v>403</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="8">
         <v>426</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="8">
         <v>451</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="8">
         <v>470</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" t="s" s="8">
         <v>488</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" t="s" s="8">
         <v>508</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="8">
         <v>532</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" t="s" s="8">
         <v>554</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="s" s="8">
         <v>579</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="s" s="8">
         <v>598</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" t="s" s="8">
         <v>617</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A10" t="s" s="7">
         <v>104</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="8">
         <v>380</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="8">
         <v>404</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="8">
         <v>427</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="8">
         <v>452</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="8">
         <v>471</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" t="s" s="8">
         <v>489</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" t="s" s="8">
         <v>509</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" t="s" s="8">
         <v>533</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" t="s" s="8">
         <v>555</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="s" s="8">
         <v>580</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" t="s" s="8">
         <v>599</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" t="s" s="8">
         <v>618</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A11" t="s" s="7">
         <v>105</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="8">
         <v>381</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="8">
         <v>405</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="8">
         <v>428</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="8">
         <v>453</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="8">
         <v>220</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" t="s" s="8">
         <v>490</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" t="s" s="8">
         <v>510</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" t="s" s="8">
         <v>534</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" t="s" s="8">
         <v>556</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="s" s="8">
         <v>581</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" t="s" s="8">
         <v>600</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" t="s" s="8">
         <v>619</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A12" t="s" s="7">
         <v>106</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="8">
         <v>382</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="8">
         <v>406</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="8">
         <v>429</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="8">
         <v>454</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="8">
         <v>472</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" t="s" s="8">
         <v>491</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" t="s" s="8">
         <v>511</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" t="s" s="8">
         <v>535</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" t="s" s="8">
         <v>557</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" t="s" s="8">
         <v>582</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" t="s" s="8">
         <v>601</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" t="s" s="8">
         <v>620</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
+    <row r="13" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A13" t="s" s="7">
         <v>107</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="8">
         <v>383</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="8">
         <v>407</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="8">
         <v>430</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="8">
         <v>455</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="8">
         <v>473</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="8">
         <v>492</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="s" s="8">
         <v>512</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" t="s" s="8">
         <v>536</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" t="s" s="8">
         <v>558</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="s" s="8">
         <v>583</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" t="s" s="8">
         <v>602</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" t="s" s="8">
         <v>621</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
+    <row r="14" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A14" t="s" s="7">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="8">
         <v>384</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="8">
         <v>408</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="8">
         <v>431</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="8">
         <v>456</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="8">
         <v>474</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="8">
         <v>493</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" t="s" s="8">
         <v>513</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" t="s" s="8">
         <v>537</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" t="s" s="8">
         <v>559</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="s" s="8">
         <v>584</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" t="s" s="8">
         <v>603</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" t="s" s="8">
         <v>622</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A15" t="s" s="7">
         <v>372</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="8">
         <v>385</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="8">
         <v>409</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="8">
         <v>432</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="8">
         <v>457</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="8">
         <v>475</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="8">
         <v>494</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" t="s" s="8">
         <v>514</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" t="s" s="8">
         <v>538</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" t="s" s="8">
         <v>560</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" t="s" s="8">
         <v>585</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" t="s" s="8">
         <v>604</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" t="s" s="8">
         <v>623</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A16" t="s" s="7">
         <v>109</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="8">
         <v>386</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="8">
         <v>410</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="8">
         <v>433</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="8">
         <v>458</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="8">
         <v>476</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="8">
         <v>495</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" t="s" s="8">
         <v>515</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" t="s" s="8">
         <v>383</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" t="s" s="8">
         <v>561</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" t="s" s="8">
         <v>586</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" t="s" s="8">
         <v>605</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" t="s" s="8">
         <v>624</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A17" t="s" s="7">
         <v>110</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="8">
         <v>387</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="8">
         <v>411</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="8">
         <v>434</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="8">
         <v>459</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="8">
         <v>477</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="8">
         <v>496</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" t="s" s="8">
         <v>516</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" t="s" s="8">
         <v>539</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" t="s" s="8">
         <v>562</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" t="s" s="8">
         <v>587</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" t="s" s="8">
         <v>606</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" t="s" s="8">
         <v>625</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
+    <row r="18" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A18" t="s" s="7">
         <v>111</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="8">
         <v>388</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="8">
         <v>412</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="8">
         <v>435</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="8">
         <v>460</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="s" s="8">
         <v>478</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" t="s" s="8">
         <v>497</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" t="s" s="8">
         <v>517</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" t="s" s="8">
         <v>540</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" t="s" s="8">
         <v>563</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" t="s" s="8">
         <v>588</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" t="s" s="8">
         <v>607</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" t="s" s="8">
         <v>626</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
+    <row r="19" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A19" t="s" s="7">
         <v>112</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="8">
         <v>389</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="8">
         <v>413</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="8">
         <v>436</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" t="s" s="8">
         <v>518</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" t="s" s="8">
         <v>541</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" t="s" s="8">
         <v>564</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
+    <row r="20" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A20" t="s" s="7">
         <v>113</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="8">
         <v>390</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="8">
         <v>414</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="8">
         <v>437</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="8">
         <v>461</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="8">
         <v>479</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" t="s" s="8">
         <v>498</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" t="s" s="8">
         <v>519</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" t="s" s="8">
         <v>542</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" t="s" s="8">
         <v>565</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="s" s="8">
         <v>589</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" t="s" s="8">
         <v>608</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" t="s" s="8">
         <v>627</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
+    <row r="21" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A21" t="s" s="7">
         <v>114</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="8">
         <v>391</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="8">
         <v>415</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="8">
         <v>438</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="8">
         <v>462</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="8">
         <v>480</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" t="s" s="8">
         <v>499</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" t="s" s="8">
         <v>520</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" t="s" s="8">
         <v>543</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" t="s" s="8">
         <v>566</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" t="s" s="8">
         <v>590</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" t="s" s="8">
         <v>609</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" t="s" s="8">
         <v>628</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
+    <row r="22" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A22" t="s" s="7">
         <v>115</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="8">
         <v>392</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="8">
         <v>416</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="8">
         <v>439</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="8">
         <v>463</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" t="s" s="8">
         <v>481</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" t="s" s="8">
         <v>500</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" t="s" s="8">
         <v>521</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" t="s" s="8">
         <v>544</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" t="s" s="8">
         <v>567</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" t="s" s="8">
         <v>591</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" t="s" s="8">
         <v>610</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" t="s" s="8">
         <v>629</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
+    <row r="23" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A23" t="s" s="7">
         <v>116</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="8">
         <v>393</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="8">
         <v>417</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="8">
         <v>440</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="s" s="8">
         <v>522</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="8">
         <v>545</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" t="s" s="8">
         <v>568</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
+    <row r="24" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A24" t="s" s="7">
         <v>117</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="8">
         <v>394</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="8">
         <v>418</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="8">
         <v>441</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" t="s" s="8">
         <v>464</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" t="s" s="8">
         <v>482</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" t="s" s="8">
         <v>501</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" t="s" s="8">
         <v>523</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" t="s" s="8">
         <v>546</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" t="s" s="8">
         <v>569</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" t="s" s="8">
         <v>592</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" t="s" s="8">
         <v>611</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" t="s" s="8">
         <v>630</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
+    <row r="25" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A25" t="s" s="7">
         <v>118</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="8">
         <v>395</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="8">
         <v>416</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="8">
         <v>442</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" t="s" s="8">
         <v>524</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" t="s" s="8">
         <v>547</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" t="s" s="8">
         <v>570</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
+    <row r="26" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A26" t="s" s="7">
         <v>119</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="8">
         <v>396</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" t="s" s="8">
         <v>419</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="s" s="8">
         <v>443</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" t="s" s="8">
         <v>465</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" t="s" s="8">
         <v>483</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" t="s" s="8">
         <v>502</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" t="s" s="8">
         <v>525</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" t="s" s="8">
         <v>548</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" t="s" s="8">
         <v>571</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" t="s" s="8">
         <v>593</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" t="s" s="8">
         <v>612</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" t="s" s="8">
         <v>631</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
+    <row r="27" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A27" t="s" s="7">
         <v>120</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="8">
         <v>397</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" t="s" s="8">
         <v>420</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="8">
         <v>444</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" t="s" s="8">
         <v>526</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" t="s" s="8">
         <v>549</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" t="s" s="8">
         <v>572</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
+    <row r="28" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A28" t="s" s="7">
         <v>121</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="8">
         <v>398</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" t="s" s="8">
         <v>421</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" t="s" s="8">
         <v>445</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" t="s" s="8">
         <v>527</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" t="s" s="8">
         <v>550</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" t="s" s="8">
         <v>573</v>
       </c>
     </row>
@@ -12759,1065 +12809,1076 @@
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
-    <col min="2" max="13" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" ht="36.0" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="8" t="s">
         <v>632</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="8" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="8" t="s">
         <v>633</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A4" t="s" s="7">
         <v>98</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="8">
         <v>634</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="8">
         <v>634</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="8">
         <v>634</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="8">
         <v>194</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="8">
         <v>194</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="8">
         <v>194</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="8">
         <v>764</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="8">
         <v>764</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="8">
         <v>764</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="s" s="8">
         <v>836</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" t="s" s="8">
         <v>836</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" t="s" s="8">
         <v>836</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A5" t="s" s="7">
         <v>99</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="8">
         <v>635</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="8">
         <v>659</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="8">
         <v>683</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="8">
         <v>707</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="8">
         <v>726</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="8">
         <v>745</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="8">
         <v>765</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="8">
         <v>659</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="8">
         <v>812</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="8">
         <v>837</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" t="s" s="8">
         <v>855</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" t="s" s="8">
         <v>874</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A6" t="s" s="7">
         <v>100</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="8">
         <v>636</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="8">
         <v>660</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="8">
         <v>684</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="8">
         <v>708</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="8">
         <v>727</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="8">
         <v>746</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" t="s" s="8">
         <v>766</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="8">
         <v>789</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" t="s" s="8">
         <v>813</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="8">
         <v>838</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" t="s" s="8">
         <v>856</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" t="s" s="8">
         <v>875</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A7" t="s" s="7">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="8">
         <v>637</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="8">
         <v>661</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="8">
         <v>685</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="8">
         <v>709</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="8">
         <v>728</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" t="s" s="8">
         <v>747</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" t="s" s="8">
         <v>767</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="8">
         <v>790</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" t="s" s="8">
         <v>814</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="s" s="8">
         <v>839</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="s" s="8">
         <v>857</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" t="s" s="8">
         <v>876</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A8" t="s" s="7">
         <v>102</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="8">
         <v>638</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="8">
         <v>662</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="8">
         <v>686</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="8">
         <v>710</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="8">
         <v>729</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" t="s" s="8">
         <v>748</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" t="s" s="8">
         <v>768</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="8">
         <v>791</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" t="s" s="8">
         <v>815</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" t="s" s="8">
         <v>840</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" t="s" s="8">
         <v>858</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" t="s" s="8">
         <v>877</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A9" t="s" s="7">
         <v>103</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="8">
         <v>639</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="8">
         <v>663</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="8">
         <v>687</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="8">
         <v>711</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="8">
         <v>730</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" t="s" s="8">
         <v>749</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" t="s" s="8">
         <v>769</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="8">
         <v>792</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" t="s" s="8">
         <v>816</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="s" s="8">
         <v>841</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="s" s="8">
         <v>859</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" t="s" s="8">
         <v>878</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A10" t="s" s="7">
         <v>104</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="8">
         <v>640</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="8">
         <v>664</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="8">
         <v>688</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="8">
         <v>712</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="8">
         <v>731</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" t="s" s="8">
         <v>750</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" t="s" s="8">
         <v>770</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" t="s" s="8">
         <v>793</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" t="s" s="8">
         <v>817</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="s" s="8">
         <v>842</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" t="s" s="8">
         <v>860</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" t="s" s="8">
         <v>879</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A11" t="s" s="7">
         <v>105</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="8">
         <v>641</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="8">
         <v>665</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="8">
         <v>689</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="8">
         <v>713</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="8">
         <v>732</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" t="s" s="8">
         <v>751</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" t="s" s="8">
         <v>771</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" t="s" s="8">
         <v>794</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" t="s" s="8">
         <v>818</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="s" s="8">
         <v>843</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" t="s" s="8">
         <v>861</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" t="s" s="8">
         <v>880</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A12" t="s" s="7">
         <v>106</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="8">
         <v>642</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="8">
         <v>666</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="8">
         <v>690</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="8">
         <v>714</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="8">
         <v>733</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" t="s" s="8">
         <v>752</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" t="s" s="8">
         <v>772</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" t="s" s="8">
         <v>795</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" t="s" s="8">
         <v>819</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" t="s" s="8">
         <v>844</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" t="s" s="8">
         <v>862</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" t="s" s="8">
         <v>881</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
+    <row r="13" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A13" t="s" s="7">
         <v>107</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="8">
         <v>643</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="8">
         <v>667</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="8">
         <v>691</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="8">
         <v>715</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="8">
         <v>734</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="8">
         <v>753</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="s" s="8">
         <v>773</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" t="s" s="8">
         <v>796</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" t="s" s="8">
         <v>820</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="s" s="8">
         <v>845</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" t="s" s="8">
         <v>863</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" t="s" s="8">
         <v>461</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
+    <row r="14" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A14" t="s" s="7">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="8">
         <v>644</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="8">
         <v>668</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="8">
         <v>692</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="8">
         <v>716</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="8">
         <v>735</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="8">
         <v>754</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" t="s" s="8">
         <v>774</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" t="s" s="8">
         <v>797</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" t="s" s="8">
         <v>821</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="s" s="8">
         <v>846</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" t="s" s="8">
         <v>864</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" t="s" s="8">
         <v>882</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A15" t="s" s="7">
         <v>372</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="8">
         <v>645</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="8">
         <v>669</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="8">
         <v>693</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="8">
         <v>717</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="8">
         <v>736</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="8">
         <v>755</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" t="s" s="8">
         <v>775</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" t="s" s="8">
         <v>798</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" t="s" s="8">
         <v>822</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" t="s" s="8">
         <v>847</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" t="s" s="8">
         <v>865</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" t="s" s="8">
         <v>883</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A16" t="s" s="7">
         <v>109</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="8">
         <v>646</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="8">
         <v>670</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="8">
         <v>694</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="8">
         <v>718</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="8">
         <v>737</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="8">
         <v>756</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" t="s" s="8">
         <v>776</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" t="s" s="8">
         <v>799</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" t="s" s="8">
         <v>823</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" t="s" s="8">
         <v>848</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" t="s" s="8">
         <v>866</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" t="s" s="8">
         <v>884</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A17" t="s" s="7">
         <v>110</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="8">
         <v>647</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="8">
         <v>671</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="8">
         <v>695</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="8">
         <v>719</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="8">
         <v>738</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="8">
         <v>757</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" t="s" s="8">
         <v>777</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" t="s" s="8">
         <v>800</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" t="s" s="8">
         <v>824</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" t="s" s="8">
         <v>849</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" t="s" s="8">
         <v>867</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" t="s" s="8">
         <v>885</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
+    <row r="18" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A18" t="s" s="7">
         <v>111</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="8">
         <v>648</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="8">
         <v>672</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="8">
         <v>696</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="8">
         <v>720</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="s" s="8">
         <v>739</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" t="s" s="8">
         <v>758</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" t="s" s="8">
         <v>778</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" t="s" s="8">
         <v>801</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" t="s" s="8">
         <v>825</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" t="s" s="8">
         <v>850</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" t="s" s="8">
         <v>868</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" t="s" s="8">
         <v>886</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
+    <row r="19" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A19" t="s" s="7">
         <v>112</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="8">
         <v>649</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="8">
         <v>673</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="8">
         <v>697</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" t="s" s="8">
         <v>779</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" t="s" s="8">
         <v>802</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" t="s" s="8">
         <v>826</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
+    <row r="20" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A20" t="s" s="7">
         <v>113</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="8">
         <v>650</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="8">
         <v>674</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="8">
         <v>698</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="8">
         <v>721</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="8">
         <v>740</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" t="s" s="8">
         <v>759</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" t="s" s="8">
         <v>780</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" t="s" s="8">
         <v>803</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" t="s" s="8">
         <v>827</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="s" s="8">
         <v>851</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" t="s" s="8">
         <v>869</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" t="s" s="8">
         <v>887</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
+    <row r="21" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A21" t="s" s="7">
         <v>114</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="8">
         <v>651</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="8">
         <v>675</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="8">
         <v>699</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="8">
         <v>722</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="8">
         <v>741</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" t="s" s="8">
         <v>760</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" t="s" s="8">
         <v>781</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" t="s" s="8">
         <v>804</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" t="s" s="8">
         <v>828</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" t="s" s="8">
         <v>852</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" t="s" s="8">
         <v>870</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" t="s" s="8">
         <v>888</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
+    <row r="22" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A22" t="s" s="7">
         <v>115</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="8">
         <v>652</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="8">
         <v>676</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="8">
         <v>700</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="8">
         <v>723</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" t="s" s="8">
         <v>742</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" t="s" s="8">
         <v>761</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" t="s" s="8">
         <v>782</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" t="s" s="8">
         <v>805</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" t="s" s="8">
         <v>829</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" t="s" s="8">
         <v>853</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" t="s" s="8">
         <v>871</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" t="s" s="8">
         <v>889</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
+    <row r="23" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A23" t="s" s="7">
         <v>116</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="8">
         <v>653</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="8">
         <v>677</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="8">
         <v>701</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="s" s="8">
         <v>783</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="8">
         <v>806</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" t="s" s="8">
         <v>830</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
+    <row r="24" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A24" t="s" s="7">
         <v>117</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="8">
         <v>654</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="8">
         <v>678</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="8">
         <v>702</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" t="s" s="8">
         <v>724</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" t="s" s="8">
         <v>743</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" t="s" s="8">
         <v>762</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" t="s" s="8">
         <v>784</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" t="s" s="8">
         <v>807</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" t="s" s="8">
         <v>831</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" t="s" s="8">
         <v>854</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" t="s" s="8">
         <v>872</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" t="s" s="8">
         <v>890</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
+    <row r="25" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A25" t="s" s="7">
         <v>118</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="8">
         <v>655</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="8">
         <v>679</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="8">
         <v>703</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" t="s" s="8">
         <v>785</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" t="s" s="8">
         <v>808</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" t="s" s="8">
         <v>832</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
+    <row r="26" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A26" t="s" s="7">
         <v>119</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="8">
         <v>656</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" t="s" s="8">
         <v>680</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="s" s="8">
         <v>704</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" t="s" s="8">
         <v>725</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" t="s" s="8">
         <v>744</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" t="s" s="8">
         <v>763</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" t="s" s="8">
         <v>786</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" t="s" s="8">
         <v>809</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" t="s" s="8">
         <v>833</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" t="s" s="8">
         <v>526</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" t="s" s="8">
         <v>873</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" t="s" s="8">
         <v>891</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
+    <row r="27" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A27" t="s" s="7">
         <v>120</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="8">
         <v>657</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" t="s" s="8">
         <v>681</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="8">
         <v>705</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" t="s" s="8">
         <v>787</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" t="s" s="8">
         <v>810</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" t="s" s="8">
         <v>834</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
+    <row r="28" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A28" t="s" s="7">
         <v>121</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="8">
         <v>658</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" t="s" s="8">
         <v>682</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" t="s" s="8">
         <v>706</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" t="s" s="8">
         <v>788</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" t="s" s="8">
         <v>811</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" t="s" s="8">
         <v>835</v>
       </c>
     </row>
@@ -13835,1065 +13896,1076 @@
   <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
-    <col min="2" max="13" width="45.7109375" customWidth="1"/>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="24" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="24" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:13" ht="36.0" customHeight="1">
+      <c r="A1" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="4" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="8" t="s">
         <v>892</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="8" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="3" spans="1:13" s="1" customFormat="1" ht="45" customHeight="1">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13" s="1" customFormat="1" ht="45.0" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="8" t="s">
         <v>893</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="8" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" t="s">
+    <row r="4" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A4" t="s" s="7">
         <v>98</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" t="s" s="8">
         <v>894</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" t="s" s="8">
         <v>894</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" t="s" s="8">
         <v>894</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" t="s" s="8">
         <v>963</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" t="s" s="8">
         <v>963</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" t="s" s="8">
         <v>963</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" t="s" s="8">
         <v>1021</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" t="s" s="8">
         <v>1021</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" t="s" s="8">
         <v>1021</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" t="s" s="8">
         <v>1088</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" t="s" s="8">
         <v>1088</v>
       </c>
-      <c r="M4" t="s">
+      <c r="M4" t="s" s="8">
         <v>1088</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" t="s">
+    <row r="5" spans="1:13" ht="18.0" customHeight="1">
+      <c r="A5" t="s" s="7">
         <v>99</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" t="s" s="8">
         <v>895</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" t="s" s="8">
         <v>918</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" t="s" s="8">
         <v>939</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" t="s" s="8">
         <v>964</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" t="s" s="8">
         <v>983</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" t="s" s="8">
         <v>1002</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" t="s" s="8">
         <v>1022</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" t="s" s="8">
         <v>964</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" t="s" s="8">
         <v>1068</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" t="s" s="8">
         <v>1089</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" t="s" s="8">
         <v>1107</v>
       </c>
-      <c r="M5" t="s">
+      <c r="M5" t="s" s="8">
         <v>1126</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" t="s">
+    <row r="6" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A6" t="s" s="7">
         <v>100</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="8">
         <v>896</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="8">
         <v>199</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" t="s" s="8">
         <v>940</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" t="s" s="8">
         <v>965</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" t="s" s="8">
         <v>984</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" t="s" s="8">
         <v>1003</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" t="s" s="8">
         <v>1023</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" t="s" s="8">
         <v>1046</v>
       </c>
-      <c r="J6" t="s">
+      <c r="J6" t="s" s="8">
         <v>1055</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" t="s" s="8">
         <v>1090</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" t="s" s="8">
         <v>1108</v>
       </c>
-      <c r="M6" t="s">
+      <c r="M6" t="s" s="8">
         <v>1127</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" t="s">
+    <row r="7" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A7" t="s" s="7">
         <v>101</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="8">
         <v>897</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="8">
         <v>919</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" t="s" s="8">
         <v>941</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" t="s" s="8">
         <v>966</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" t="s" s="8">
         <v>985</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G7" t="s" s="8">
         <v>1004</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" t="s" s="8">
         <v>1024</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" t="s" s="8">
         <v>1047</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J7" t="s" s="8">
         <v>1069</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K7" t="s" s="8">
         <v>1091</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" t="s" s="8">
         <v>1109</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" t="s" s="8">
         <v>1128</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
+    <row r="8" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A8" t="s" s="7">
         <v>102</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" t="s" s="8">
         <v>898</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" t="s" s="8">
         <v>920</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" t="s" s="8">
         <v>942</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" t="s" s="8">
         <v>967</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="s" s="8">
         <v>986</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" t="s" s="8">
         <v>1005</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" t="s" s="8">
         <v>1025</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" t="s" s="8">
         <v>1048</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" t="s" s="8">
         <v>1070</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" t="s" s="8">
         <v>1092</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" t="s" s="8">
         <v>1110</v>
       </c>
-      <c r="M8" t="s">
+      <c r="M8" t="s" s="8">
         <v>1129</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
-      <c r="A9" t="s">
+    <row r="9" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A9" t="s" s="7">
         <v>103</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" t="s" s="8">
         <v>899</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" t="s" s="8">
         <v>921</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" t="s" s="8">
         <v>943</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" t="s" s="8">
         <v>968</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" t="s" s="8">
         <v>987</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" t="s" s="8">
         <v>1006</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" t="s" s="8">
         <v>1026</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I9" t="s" s="8">
         <v>1049</v>
       </c>
-      <c r="J9" t="s">
+      <c r="J9" t="s" s="8">
         <v>1071</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K9" t="s" s="8">
         <v>1093</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" t="s" s="8">
         <v>1111</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" t="s" s="8">
         <v>1130</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" t="s">
+    <row r="10" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A10" t="s" s="7">
         <v>104</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" t="s" s="8">
         <v>900</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" t="s" s="8">
         <v>152</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" t="s" s="8">
         <v>944</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" t="s" s="8">
         <v>969</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" t="s" s="8">
         <v>988</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" t="s" s="8">
         <v>1007</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" t="s" s="8">
         <v>1027</v>
       </c>
-      <c r="I10" t="s">
+      <c r="I10" t="s" s="8">
         <v>1050</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" t="s" s="8">
         <v>1072</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" t="s" s="8">
         <v>1094</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" t="s" s="8">
         <v>1112</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" t="s" s="8">
         <v>1131</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
-      <c r="A11" t="s">
+    <row r="11" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A11" t="s" s="7">
         <v>105</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" t="s" s="8">
         <v>901</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" t="s" s="8">
         <v>922</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" t="s" s="8">
         <v>945</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" t="s" s="8">
         <v>970</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" t="s" s="8">
         <v>989</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G11" t="s" s="8">
         <v>1008</v>
       </c>
-      <c r="H11" t="s">
+      <c r="H11" t="s" s="8">
         <v>1028</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I11" t="s" s="8">
         <v>1051</v>
       </c>
-      <c r="J11" t="s">
+      <c r="J11" t="s" s="8">
         <v>1073</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" t="s" s="8">
         <v>1095</v>
       </c>
-      <c r="L11" t="s">
+      <c r="L11" t="s" s="8">
         <v>1113</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" t="s" s="8">
         <v>1132</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
-      <c r="A12" t="s">
+    <row r="12" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A12" t="s" s="7">
         <v>106</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" t="s" s="8">
         <v>902</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" t="s" s="8">
         <v>923</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" t="s" s="8">
         <v>946</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" t="s" s="8">
         <v>971</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" t="s" s="8">
         <v>990</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" t="s" s="8">
         <v>1009</v>
       </c>
-      <c r="H12" t="s">
+      <c r="H12" t="s" s="8">
         <v>1029</v>
       </c>
-      <c r="I12" t="s">
+      <c r="I12" t="s" s="8">
         <v>130</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" t="s" s="8">
         <v>1074</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" t="s" s="8">
         <v>1096</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" t="s" s="8">
         <v>1114</v>
       </c>
-      <c r="M12" t="s">
+      <c r="M12" t="s" s="8">
         <v>1133</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
+    <row r="13" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A13" t="s" s="7">
         <v>107</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" t="s" s="8">
         <v>903</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" t="s" s="8">
         <v>924</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" t="s" s="8">
         <v>947</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" t="s" s="8">
         <v>972</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" t="s" s="8">
         <v>991</v>
       </c>
-      <c r="G13" t="s">
+      <c r="G13" t="s" s="8">
         <v>1010</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" t="s" s="8">
         <v>1030</v>
       </c>
-      <c r="I13" t="s">
+      <c r="I13" t="s" s="8">
         <v>1052</v>
       </c>
-      <c r="J13" t="s">
+      <c r="J13" t="s" s="8">
         <v>1075</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" t="s" s="8">
         <v>1097</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" t="s" s="8">
         <v>1115</v>
       </c>
-      <c r="M13" t="s">
+      <c r="M13" t="s" s="8">
         <v>1134</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
-      <c r="A14" t="s">
+    <row r="14" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A14" t="s" s="7">
         <v>108</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" t="s" s="8">
         <v>904</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" t="s" s="8">
         <v>380</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" t="s" s="8">
         <v>948</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" t="s" s="8">
         <v>973</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" t="s" s="8">
         <v>992</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" t="s" s="8">
         <v>1011</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H14" t="s" s="8">
         <v>1031</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" t="s" s="8">
         <v>1053</v>
       </c>
-      <c r="J14" t="s">
+      <c r="J14" t="s" s="8">
         <v>1076</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" t="s" s="8">
         <v>1098</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" t="s" s="8">
         <v>1116</v>
       </c>
-      <c r="M14" t="s">
+      <c r="M14" t="s" s="8">
         <v>1135</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
-      <c r="A15" t="s">
+    <row r="15" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A15" t="s" s="7">
         <v>372</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" t="s" s="8">
         <v>905</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" t="s" s="8">
         <v>925</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" t="s" s="8">
         <v>949</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" t="s" s="8">
         <v>974</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" t="s" s="8">
         <v>993</v>
       </c>
-      <c r="G15" t="s">
+      <c r="G15" t="s" s="8">
         <v>1012</v>
       </c>
-      <c r="H15" t="s">
+      <c r="H15" t="s" s="8">
         <v>1032</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" t="s" s="8">
         <v>1054</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" t="s" s="8">
         <v>1077</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" t="s" s="8">
         <v>137</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" t="s" s="8">
         <v>1117</v>
       </c>
-      <c r="M15" t="s">
+      <c r="M15" t="s" s="8">
         <v>1136</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
-      <c r="A16" t="s">
+    <row r="16" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A16" t="s" s="7">
         <v>109</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" t="s" s="8">
         <v>906</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" t="s" s="8">
         <v>926</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" t="s" s="8">
         <v>950</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" t="s" s="8">
         <v>975</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" t="s" s="8">
         <v>994</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" t="s" s="8">
         <v>1013</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" t="s" s="8">
         <v>1033</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" t="s" s="8">
         <v>1055</v>
       </c>
-      <c r="J16" t="s">
+      <c r="J16" t="s" s="8">
         <v>1078</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" t="s" s="8">
         <v>1099</v>
       </c>
-      <c r="L16" t="s">
+      <c r="L16" t="s" s="8">
         <v>1118</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" t="s" s="8">
         <v>1137</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
-      <c r="A17" t="s">
+    <row r="17" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A17" t="s" s="7">
         <v>110</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" t="s" s="8">
         <v>907</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" t="s" s="8">
         <v>927</v>
       </c>
-      <c r="D17" t="s">
+      <c r="D17" t="s" s="8">
         <v>951</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E17" t="s" s="8">
         <v>976</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" t="s" s="8">
         <v>995</v>
       </c>
-      <c r="G17" t="s">
+      <c r="G17" t="s" s="8">
         <v>1014</v>
       </c>
-      <c r="H17" t="s">
+      <c r="H17" t="s" s="8">
         <v>1034</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" t="s" s="8">
         <v>1056</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" t="s" s="8">
         <v>1079</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" t="s" s="8">
         <v>1100</v>
       </c>
-      <c r="L17" t="s">
+      <c r="L17" t="s" s="8">
         <v>1119</v>
       </c>
-      <c r="M17" t="s">
+      <c r="M17" t="s" s="8">
         <v>1138</v>
       </c>
     </row>
-    <row r="18" spans="1:13">
-      <c r="A18" t="s">
+    <row r="18" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A18" t="s" s="7">
         <v>111</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" t="s" s="8">
         <v>908</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" t="s" s="8">
         <v>928</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" t="s" s="8">
         <v>952</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E18" t="s" s="8">
         <v>977</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" t="s" s="8">
         <v>996</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" t="s" s="8">
         <v>1015</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H18" t="s" s="8">
         <v>1035</v>
       </c>
-      <c r="I18" t="s">
+      <c r="I18" t="s" s="8">
         <v>1057</v>
       </c>
-      <c r="J18" t="s">
+      <c r="J18" t="s" s="8">
         <v>1080</v>
       </c>
-      <c r="K18" t="s">
+      <c r="K18" t="s" s="8">
         <v>1101</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" t="s" s="8">
         <v>1120</v>
       </c>
-      <c r="M18" t="s">
+      <c r="M18" t="s" s="8">
         <v>1139</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
-      <c r="A19" t="s">
+    <row r="19" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A19" t="s" s="7">
         <v>112</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" t="s" s="8">
         <v>909</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" t="s" s="8">
         <v>929</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" t="s" s="8">
         <v>953</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H19" t="s" s="8">
         <v>1036</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I19" t="s" s="8">
         <v>1058</v>
       </c>
-      <c r="J19" t="s">
+      <c r="J19" t="s" s="8">
         <v>1081</v>
       </c>
     </row>
-    <row r="20" spans="1:13">
-      <c r="A20" t="s">
+    <row r="20" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A20" t="s" s="7">
         <v>113</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" t="s" s="8">
         <v>910</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" t="s" s="8">
         <v>930</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" t="s" s="8">
         <v>954</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E20" t="s" s="8">
         <v>978</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" t="s" s="8">
         <v>997</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" t="s" s="8">
         <v>1016</v>
       </c>
-      <c r="H20" t="s">
+      <c r="H20" t="s" s="8">
         <v>1037</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" t="s" s="8">
         <v>1059</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" t="s" s="8">
         <v>1082</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K20" t="s" s="8">
         <v>1102</v>
       </c>
-      <c r="L20" t="s">
+      <c r="L20" t="s" s="8">
         <v>1121</v>
       </c>
-      <c r="M20" t="s">
+      <c r="M20" t="s" s="8">
         <v>1140</v>
       </c>
     </row>
-    <row r="21" spans="1:13">
-      <c r="A21" t="s">
+    <row r="21" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A21" t="s" s="7">
         <v>114</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" t="s" s="8">
         <v>911</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" t="s" s="8">
         <v>931</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D21" t="s" s="8">
         <v>955</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" t="s" s="8">
         <v>979</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" t="s" s="8">
         <v>998</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G21" t="s" s="8">
         <v>1017</v>
       </c>
-      <c r="H21" t="s">
+      <c r="H21" t="s" s="8">
         <v>1038</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" t="s" s="8">
         <v>1060</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" t="s" s="8">
         <v>1083</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" t="s" s="8">
         <v>1103</v>
       </c>
-      <c r="L21" t="s">
+      <c r="L21" t="s" s="8">
         <v>1122</v>
       </c>
-      <c r="M21" t="s">
+      <c r="M21" t="s" s="8">
         <v>1141</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
-      <c r="A22" t="s">
+    <row r="22" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A22" t="s" s="7">
         <v>115</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" t="s" s="8">
         <v>912</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" t="s" s="8">
         <v>932</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D22" t="s" s="8">
         <v>956</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E22" t="s" s="8">
         <v>980</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" t="s" s="8">
         <v>999</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G22" t="s" s="8">
         <v>1018</v>
       </c>
-      <c r="H22" t="s">
+      <c r="H22" t="s" s="8">
         <v>1039</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" t="s" s="8">
         <v>1061</v>
       </c>
-      <c r="J22" t="s">
+      <c r="J22" t="s" s="8">
         <v>678</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" t="s" s="8">
         <v>1104</v>
       </c>
-      <c r="L22" t="s">
+      <c r="L22" t="s" s="8">
         <v>1123</v>
       </c>
-      <c r="M22" t="s">
+      <c r="M22" t="s" s="8">
         <v>1142</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
-      <c r="A23" t="s">
+    <row r="23" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A23" t="s" s="7">
         <v>116</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" t="s" s="8">
         <v>161</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" t="s" s="8">
         <v>933</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D23" t="s" s="8">
         <v>957</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H23" t="s" s="8">
         <v>1040</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" t="s" s="8">
         <v>1062</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" t="s" s="8">
         <v>1084</v>
       </c>
     </row>
-    <row r="24" spans="1:13">
-      <c r="A24" t="s">
+    <row r="24" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A24" t="s" s="7">
         <v>117</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" t="s" s="8">
         <v>913</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" t="s" s="8">
         <v>934</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D24" t="s" s="8">
         <v>958</v>
       </c>
-      <c r="E24" t="s">
+      <c r="E24" t="s" s="8">
         <v>981</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F24" t="s" s="8">
         <v>1000</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" t="s" s="8">
         <v>1019</v>
       </c>
-      <c r="H24" t="s">
+      <c r="H24" t="s" s="8">
         <v>1041</v>
       </c>
-      <c r="I24" t="s">
+      <c r="I24" t="s" s="8">
         <v>1063</v>
       </c>
-      <c r="J24" t="s">
+      <c r="J24" t="s" s="8">
         <v>1085</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" t="s" s="8">
         <v>1105</v>
       </c>
-      <c r="L24" t="s">
+      <c r="L24" t="s" s="8">
         <v>1124</v>
       </c>
-      <c r="M24" t="s">
+      <c r="M24" t="s" s="8">
         <v>1143</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
-      <c r="A25" t="s">
+    <row r="25" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A25" t="s" s="7">
         <v>118</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" t="s" s="8">
         <v>914</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" t="s" s="8">
         <v>935</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D25" t="s" s="8">
         <v>959</v>
       </c>
-      <c r="H25" t="s">
+      <c r="H25" t="s" s="8">
         <v>1042</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I25" t="s" s="8">
         <v>1064</v>
       </c>
-      <c r="J25" t="s">
+      <c r="J25" t="s" s="8">
         <v>1086</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
-      <c r="A26" t="s">
+    <row r="26" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A26" t="s" s="7">
         <v>119</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" t="s" s="8">
         <v>915</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" t="s" s="8">
         <v>936</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D26" t="s" s="8">
         <v>960</v>
       </c>
-      <c r="E26" t="s">
+      <c r="E26" t="s" s="8">
         <v>982</v>
       </c>
-      <c r="F26" t="s">
+      <c r="F26" t="s" s="8">
         <v>1001</v>
       </c>
-      <c r="G26" t="s">
+      <c r="G26" t="s" s="8">
         <v>1020</v>
       </c>
-      <c r="H26" t="s">
+      <c r="H26" t="s" s="8">
         <v>1043</v>
       </c>
-      <c r="I26" t="s">
+      <c r="I26" t="s" s="8">
         <v>1065</v>
       </c>
-      <c r="J26" t="s">
+      <c r="J26" t="s" s="8">
         <v>1061</v>
       </c>
-      <c r="K26" t="s">
+      <c r="K26" t="s" s="8">
         <v>1106</v>
       </c>
-      <c r="L26" t="s">
+      <c r="L26" t="s" s="8">
         <v>1125</v>
       </c>
-      <c r="M26" t="s">
+      <c r="M26" t="s" s="8">
         <v>1144</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
-      <c r="A27" t="s">
+    <row r="27" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A27" t="s" s="7">
         <v>120</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B27" t="s" s="8">
         <v>916</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" t="s" s="8">
         <v>937</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D27" t="s" s="8">
         <v>961</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" t="s" s="8">
         <v>1044</v>
       </c>
-      <c r="I27" t="s">
+      <c r="I27" t="s" s="8">
         <v>1066</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" t="s" s="8">
         <v>440</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
-      <c r="A28" t="s">
+    <row r="28" spans="1:13" ht="30.0" customHeight="1">
+      <c r="A28" t="s" s="7">
         <v>121</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B28" t="s" s="8">
         <v>917</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" t="s" s="8">
         <v>938</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D28" t="s" s="8">
         <v>962</v>
       </c>
-      <c r="H28" t="s">
+      <c r="H28" t="s" s="8">
         <v>1045</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" t="s" s="8">
         <v>1067</v>
       </c>
-      <c r="J28" t="s">
+      <c r="J28" t="s" s="8">
         <v>1087</v>
       </c>
     </row>
